--- a/public/content-import-templates/06_lesson_resources_template.xlsx
+++ b/public/content-import-templates/06_lesson_resources_template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
   <si>
     <t>06 — نموذج موارد الدرس</t>
   </si>
@@ -32,12 +32,24 @@
     <t>— الأعمدة —</t>
   </si>
   <si>
+    <t>subject_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+  </si>
+  <si>
     <t>lesson_code *</t>
   </si>
   <si>
     <t>مثال: phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>resource_code *</t>
+  </si>
+  <si>
+    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: RES-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>resource_type *</t>
   </si>
   <si>
@@ -56,10 +68,10 @@
     <t>مثال: فيديو YouTube تعليمي</t>
   </si>
   <si>
-    <t>resource_url</t>
-  </si>
-  <si>
-    <t>ملاحظة: رابط خارجي أو embed رسمي — مثال: https://www.youtube.com/watch?v=example</t>
+    <t>resource_url *</t>
+  </si>
+  <si>
+    <t>ملاحظة: إلزامي — رابط خارجي أو embed رسمي — مثال: https://www.youtube.com/watch?v=example</t>
   </si>
   <si>
     <t>resource_format</t>
@@ -149,9 +161,15 @@
     <t>⚠️ أي مورد خارجي: احترم الترخيص ولا تحذف attribution إلا إذا كان الترخيص يسمح بذلك.</t>
   </si>
   <si>
+    <t>phys-g10-aden</t>
+  </si>
+  <si>
     <t>phys-g10-u1-l1</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-01</t>
+  </si>
+  <si>
     <t>video</t>
   </si>
   <si>
@@ -182,6 +200,9 @@
     <t>رابط خارجي — تحقق من حقوق النشر</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-02</t>
+  </si>
+  <si>
     <t>mindmap</t>
   </si>
   <si>
@@ -209,6 +230,9 @@
     <t>ملف HTML محلي — RTL وجوال</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-03</t>
+  </si>
+  <si>
     <t>experiment</t>
   </si>
   <si>
@@ -233,6 +257,9 @@
     <t>embed الرابط الرسمي فقط</t>
   </si>
   <si>
+    <t>RES-PHYS-G10-U1-L1-04</t>
+  </si>
+  <si>
     <t>pdf</t>
   </si>
   <si>
@@ -252,6 +279,9 @@
   </si>
   <si>
     <t>يُرفع الملف لاحقاً عبر لوحة الإدارة</t>
+  </si>
+  <si>
+    <t>RES-PHYS-G10-U1-L1-05</t>
   </si>
   <si>
     <t>link</t>
@@ -670,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -807,97 +837,113 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B20" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -908,25 +954,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -966,214 +1013,250 @@
       <c r="M1" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" t="s">
+        <v>79</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="I6" t="s">
         <v>57</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" t="s">
         <v>58</v>
       </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L5" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
         <v>5</v>
       </c>
-      <c r="K6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" t="s">
-        <v>85</v>
-      </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>94</v>
+      </c>
+      <c r="N6" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/public/content-import-templates/06_lesson_resources_template.xlsx
+++ b/public/content-import-templates/06_lesson_resources_template.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="تعليمات" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="موارد الدرس" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="مرجع الأكواد" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="موارد الدرس" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
   <si>
     <t>06 — نموذج موارد الدرس</t>
   </si>
@@ -35,19 +36,19 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: phys-g10-aden</t>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-aden-001</t>
   </si>
   <si>
     <t>lesson_code *</t>
   </si>
   <si>
-    <t>مثال: phys-g10-u1-l1</t>
+    <t>مثال: lesson-g10-aden-001-001</t>
   </si>
   <si>
     <t>resource_code *</t>
   </si>
   <si>
-    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: RES-PHYS-G10-U1-L1-01</t>
+    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: res-g10-aden-001-001-01</t>
   </si>
   <si>
     <t>resource_type *</t>
@@ -83,7 +84,7 @@
     <t>local_asset_path</t>
   </si>
   <si>
-    <t>ملاحظة: مسار نسبي للملف المحلي — مثال: assets/phys-g10-u1-l1-mindmap.html</t>
+    <t>ملاحظة: مسار نسبي للملف المحلي — مثال: assets/lesson-g10-aden-001-001-mindmap.html</t>
   </si>
   <si>
     <t>thumbnail_url</t>
@@ -131,7 +132,10 @@
     <t>هذه النماذج لتجهيز المحتوى قبل الاستيراد — لا تستورد بيانات فعلية من هنا تلقائياً.</t>
   </si>
   <si>
-    <t>استخدم أكواداً نصية ثابتة (snake_case أو kebab-case) — لا تستخدم UUID.</t>
+    <t>الأكواد يملكها النظام (TCS-1): نزّل القالب الجاهز من «مركز الاستيراد» ولا تكتب كوداً يدوياً.</t>
+  </si>
+  <si>
+    <t>راجع ورقة «مرجع الأكواد» داخل الملف قبل التعبئة — لا تستخدم UUID ولا حروفاً عربية في الأكواد.</t>
   </si>
   <si>
     <t>لا تضع مفاتيح API أو روابط signed أو أسرار في الملفات.</t>
@@ -161,13 +165,163 @@
     <t>⚠️ أي مورد خارجي: احترم الترخيص ولا تحذف attribution إلا إذا كان الترخيص يسمح بذلك.</t>
   </si>
   <si>
-    <t>phys-g10-aden</t>
-  </si>
-  <si>
-    <t>phys-g10-u1-l1</t>
-  </si>
-  <si>
-    <t>RES-PHYS-G10-U1-L1-01</t>
+    <t>مرجع الأكواد الرسمي — TCS-1</t>
+  </si>
+  <si>
+    <t>— صيغ الأكواد —</t>
+  </si>
+  <si>
+    <t>مادة</t>
+  </si>
+  <si>
+    <t>sub-{gradeShort}-{trackCode}-{subjectNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: sub-g10-aden-003</t>
+  </si>
+  <si>
+    <t>مجموعة مواد</t>
+  </si>
+  <si>
+    <t>grp-{gradeShort}-{trackCode}-{groupNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: grp-g10-aden-01</t>
+  </si>
+  <si>
+    <t>وحدة</t>
+  </si>
+  <si>
+    <t>unit-{gradeShort}-{trackCode}-{subjectNo:003}-{unitNo:02}</t>
+  </si>
+  <si>
+    <t>مثال: unit-g10-aden-003-02</t>
+  </si>
+  <si>
+    <t>درس</t>
+  </si>
+  <si>
+    <t>lesson-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}</t>
+  </si>
+  <si>
+    <t>مثال: lesson-g10-aden-003-004</t>
+  </si>
+  <si>
+    <t>شرح</t>
+  </si>
+  <si>
+    <t>exp-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: exp-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>مورد</t>
+  </si>
+  <si>
+    <t>res-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: res-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>تقييم</t>
+  </si>
+  <si>
+    <t>asm-{gradeShort}-{trackCode}-{subjectNo:003}-{lessonNo:003}-{seq:02}</t>
+  </si>
+  <si>
+    <t>مثال: asm-g10-aden-003-004-01</t>
+  </si>
+  <si>
+    <t>سؤال</t>
+  </si>
+  <si>
+    <t>q-{gradeShort}-{trackCode}-{subjectNo:003}-{questionNo:05}</t>
+  </si>
+  <si>
+    <t>مثال: q-g10-aden-003-00007</t>
+  </si>
+  <si>
+    <t>— القواعد —</t>
+  </si>
+  <si>
+    <t>نظام الأكواد الرسمي: TCS-1 — الأكواد يولّدها النظام ولا ينشئها المشغّل يدوياً.</t>
+  </si>
+  <si>
+    <t>الكود مستقل عن الاسم العربي: تغيير الاسم لا يغيّر الكود أبداً.</t>
+  </si>
+  <si>
+    <t>كود الدرس لا يحتوي على كود الوحدة، لذلك يمكن نقل الدرس بين الوحدات دون تغيير هويته.</t>
+  </si>
+  <si>
+    <t>كود السؤال لا يحتوي على الدرس، لأنه هوية ثابتة عبر المراجعات والاستهداف.</t>
+  </si>
+  <si>
+    <t>الصف والمسار داخل الكود مأخوذان من البيانات المرجعية الرسمية فقط.</t>
+  </si>
+  <si>
+    <t>أي كود سبق تخصيصه لا يُعاد استخدامه لكيان آخر حتى بعد الحذف.</t>
+  </si>
+  <si>
+    <t>— الصفوف المعتمدة —</t>
+  </si>
+  <si>
+    <t>g10</t>
+  </si>
+  <si>
+    <t>grade-10</t>
+  </si>
+  <si>
+    <t>الصف الأول الثانوي</t>
+  </si>
+  <si>
+    <t>g11</t>
+  </si>
+  <si>
+    <t>grade-11</t>
+  </si>
+  <si>
+    <t>الصف الثاني الثانوي</t>
+  </si>
+  <si>
+    <t>g12</t>
+  </si>
+  <si>
+    <t>grade-12</t>
+  </si>
+  <si>
+    <t>الصف الثالث الثانوي</t>
+  </si>
+  <si>
+    <t>— المسارات المعتمدة —</t>
+  </si>
+  <si>
+    <t>sanaa</t>
+  </si>
+  <si>
+    <t>منهج صنعاء</t>
+  </si>
+  <si>
+    <t>aden</t>
+  </si>
+  <si>
+    <t>منهج عدن</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>آخر</t>
+  </si>
+  <si>
+    <t>sub-g10-aden-001</t>
+  </si>
+  <si>
+    <t>lesson-g10-aden-001-001</t>
+  </si>
+  <si>
+    <t>res-g10-aden-001-001-01</t>
   </si>
   <si>
     <t>video</t>
@@ -215,7 +369,7 @@
     <t>html</t>
   </si>
   <si>
-    <t>assets/phys-g10-u1-l1-mindmap.html</t>
+    <t>assets/lesson-g10-aden-001-001-mindmap.html</t>
   </si>
   <si>
     <t>نعم</t>
@@ -245,7 +399,7 @@
     <t>https://phet.colorado.edu/sims/html/density/latest/density_all.html</t>
   </si>
   <si>
-    <t>assets/phys-g10-u1-l1-density.html</t>
+    <t>assets/lesson-g10-aden-001-001-density.html</t>
   </si>
   <si>
     <t>PhET Interactive Simulations</t>
@@ -269,7 +423,7 @@
     <t>ملف PDF للطباعة</t>
   </si>
   <si>
-    <t>assets/phys-g10-u1-l1-summary.pdf</t>
+    <t>assets/lesson-g10-aden-001-001-summary.pdf</t>
   </si>
   <si>
     <t>إنتاج داخلي</t>
@@ -700,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -946,6 +1100,14 @@
         <v>48</v>
       </c>
     </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -953,6 +1115,249 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1022,237 +1427,237 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K2" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="N2" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="O2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K3" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="N6" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="O6" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/public/content-import-templates/06_lesson_resources_template.xlsx
+++ b/public/content-import-templates/06_lesson_resources_template.xlsx
@@ -36,19 +36,19 @@
     <t>subject_code *</t>
   </si>
   <si>
-    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-aden-001</t>
+    <t>ملاحظة: إلزامي — يحدد المادة التي ينتمي إليها lesson_code — مثال: sub-g10-001</t>
   </si>
   <si>
     <t>lesson_code *</t>
   </si>
   <si>
-    <t>مثال: lesson-g10-aden-001-001</t>
+    <t>مثال: lesson-g10-001-001</t>
   </si>
   <si>
     <t>resource_code *</t>
   </si>
   <si>
-    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: res-g10-aden-001-001-01</t>
+    <t>ملاحظة: هوية ثابتة للمورد — لا تغيّرها بين الدفعات — مثال: res-g10-001-001-01</t>
   </si>
   <si>
     <t>resource_type *</t>
@@ -84,7 +84,7 @@
     <t>local_asset_path</t>
   </si>
   <si>
-    <t>ملاحظة: مسار نسبي للملف المحلي — مثال: assets/lesson-g10-aden-001-001-mindmap.html</t>
+    <t>ملاحظة: مسار نسبي للملف المحلي — مثال: assets/lesson-g10-001-001-mindmap.html</t>
   </si>
   <si>
     <t>thumbnail_url</t>
@@ -315,13 +315,13 @@
     <t>آخر</t>
   </si>
   <si>
-    <t>sub-g10-aden-001</t>
-  </si>
-  <si>
-    <t>lesson-g10-aden-001-001</t>
-  </si>
-  <si>
-    <t>res-g10-aden-001-001-01</t>
+    <t>sub-g10-001</t>
+  </si>
+  <si>
+    <t>lesson-g10-001-001</t>
+  </si>
+  <si>
+    <t>res-g10-001-001-01</t>
   </si>
   <si>
     <t>video</t>
@@ -369,7 +369,7 @@
     <t>html</t>
   </si>
   <si>
-    <t>assets/lesson-g10-aden-001-001-mindmap.html</t>
+    <t>assets/lesson-g10-001-001-mindmap.html</t>
   </si>
   <si>
     <t>نعم</t>
@@ -399,7 +399,7 @@
     <t>https://phet.colorado.edu/sims/html/density/latest/density_all.html</t>
   </si>
   <si>
-    <t>assets/lesson-g10-aden-001-001-density.html</t>
+    <t>assets/lesson-g10-001-001-density.html</t>
   </si>
   <si>
     <t>PhET Interactive Simulations</t>
@@ -423,7 +423,7 @@
     <t>ملف PDF للطباعة</t>
   </si>
   <si>
-    <t>assets/lesson-g10-aden-001-001-summary.pdf</t>
+    <t>assets/lesson-g10-001-001-summary.pdf</t>
   </si>
   <si>
     <t>إنتاج داخلي</t>

--- a/public/content-import-templates/06_lesson_resources_template.xlsx
+++ b/public/content-import-templates/06_lesson_resources_template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="151">
   <si>
     <t>06 — نموذج موارد الدرس</t>
   </si>
@@ -123,6 +123,12 @@
     <t>مثال: رابط خارجي فقط</t>
   </si>
   <si>
+    <t>is_primary</t>
+  </si>
+  <si>
+    <t>ملاحظة: نعم = هذا المورد هو محتوى الدرس نفسه (ملف PDF/Drive) — مورد واحد فقط لكل درس — مثال: لا</t>
+  </si>
+  <si>
     <t>— تعليمات عامة —</t>
   </si>
   <si>
@@ -160,6 +166,9 @@
   </si>
   <si>
     <t>video: resource_url = رابط YouTube/Vimeo — لا رفع فيديو داخل التطبيق.</t>
+  </si>
+  <si>
+    <t>is_primary=نعم: الدرس يُسلَّم كملف خارجي — يفتحه الطالب مباشرة من صفحة الدرس (يصلح لدروس PDF على Google Drive).</t>
   </si>
   <si>
     <t>⚠️ أي مورد خارجي: احترم الترخيص ولا تحذف attribution إلا إذا كان الترخيص يسمح بذلك.</t>
@@ -854,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1007,105 +1016,121 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="23" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1126,229 +1151,229 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1375,10 +1400,10 @@
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1424,244 +1449,262 @@
       <c r="O1" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N2" t="s">
+        <v>114</v>
+      </c>
+      <c r="O2" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
         <v>111</v>
       </c>
-      <c r="O2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" t="s">
-        <v>108</v>
-      </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" t="s">
         <v>120</v>
       </c>
-      <c r="N3" t="s">
-        <v>121</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="I4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" t="s">
-        <v>119</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
       <c r="M4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="P4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="P5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O6" t="s">
-        <v>147</v>
+        <v>150</v>
+      </c>
+      <c r="P6" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
